--- a/Data/Actions Simon.xlsx
+++ b/Data/Actions Simon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Zarka/Documents/Simon/Squash/Squash-Data/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8750D2-4C4A-3C49-8A49-310C76E80FE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75A8F6E-D97E-A743-9A0B-DABBFF3DE4AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3920" yWindow="940" windowWidth="30240" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actions Simon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="161">
   <si>
     <t>Points</t>
   </si>
@@ -40,15 +40,6 @@
     <t>Perdu</t>
   </si>
   <si>
-    <t>Total Gagnés</t>
-  </si>
-  <si>
-    <t>Total Perdus</t>
-  </si>
-  <si>
-    <t>Total Matchs</t>
-  </si>
-  <si>
     <t>6,277</t>
   </si>
   <si>
@@ -61,33 +52,15 @@
     <t>2</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
     <t>7,104</t>
   </si>
   <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
     <t>6,332</t>
   </si>
   <si>
     <t>Meudon Place</t>
   </si>
   <si>
-    <t>2,024</t>
-  </si>
-  <si>
     <t>5,971</t>
   </si>
   <si>
@@ -97,33 +70,15 @@
     <t>1</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
     <t>6,483</t>
   </si>
   <si>
-    <t>69%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
     <t>4,919</t>
   </si>
   <si>
     <t>Fondettes</t>
   </si>
   <si>
-    <t>2,025</t>
-  </si>
-  <si>
     <t>7,191</t>
   </si>
   <si>
@@ -139,21 +94,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>41%</t>
-  </si>
-  <si>
     <t>6,639</t>
   </si>
   <si>
@@ -406,9 +346,6 @@
     <t>538</t>
   </si>
   <si>
-    <t>Squash 95 Place</t>
-  </si>
-  <si>
     <t>893</t>
   </si>
   <si>
@@ -520,9 +457,6 @@
     <t>Levallois</t>
   </si>
   <si>
-    <t>617</t>
-  </si>
-  <si>
     <t>346</t>
   </si>
   <si>
@@ -563,6 +497,12 @@
   </si>
   <si>
     <t>Jeu de Paume</t>
+  </si>
+  <si>
+    <t>Sannois</t>
+  </si>
+  <si>
+    <t>2ème série Squash 95</t>
   </si>
 </sst>
 </file>
@@ -601,12 +541,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -948,17 +891,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="2" width="10.83203125" style="2"/>
-    <col min="3" max="3" width="10.83203125" style="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="1"/>
+    <col min="3" max="3" width="19.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,2267 +920,2564 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="B2" s="2">
+        <v>45360</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
-        <v>45538</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3" s="2">
+        <v>45360</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B4" s="2">
+        <v>45360</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45538</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45538</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>45371</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
         <v>45371</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>45371</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2">
         <v>45395</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>45395</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2">
         <v>45406</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
         <v>45406</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>45406</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
         <v>45406</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2">
         <v>45427</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2">
-        <v>45297</v>
+        <v>45444</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2">
-        <v>45297</v>
+        <v>45444</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2">
-        <v>45297</v>
+        <v>45444</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2">
-        <v>45297</v>
+        <v>45444</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2">
-        <v>45418</v>
+        <v>45449</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2">
-        <v>45510</v>
+        <v>45451</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>45510</v>
+        <v>45451</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>45510</v>
+        <v>45451</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>45510</v>
+        <v>45451</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2">
         <v>45465</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2">
         <v>45465</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B30" s="2">
         <v>45465</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2">
         <v>45465</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B32" s="2">
         <v>45468</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2">
         <v>45468</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B34" s="2">
         <v>45468</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B35" s="2">
         <v>45472</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B36" s="2">
         <v>45472</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B37" s="2">
         <v>45472</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2">
-        <v>45419</v>
+        <v>45478</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2">
-        <v>45419</v>
+        <v>45478</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2">
-        <v>45419</v>
+        <v>45478</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2">
         <v>45535</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B42" s="2">
-        <v>45300</v>
+        <v>45535</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B43" s="2">
-        <v>45300</v>
+        <v>45535</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2">
-        <v>45300</v>
+        <v>45535</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B45" s="2">
-        <v>45453</v>
+        <v>45571</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B46" s="2">
-        <v>45453</v>
+        <v>45571</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B47" s="2">
-        <v>45606</v>
+        <v>45576</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B48" s="2">
         <v>45578</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B49" s="2">
         <v>45578</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B50" s="2">
         <v>45578</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>83</v>
+      <c r="A51" s="1">
+        <v>10000</v>
       </c>
       <c r="B51" s="2">
-        <v>45591</v>
+        <v>45583</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>38</v>
+        <v>159</v>
+      </c>
+      <c r="E51" s="3">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="B52" s="2">
         <v>45591</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B53" s="2">
-        <v>45333</v>
+        <v>45591</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B54" s="2">
-        <v>45333</v>
+        <v>45598</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B55" s="2">
-        <v>45333</v>
+        <v>45598</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B56" s="2">
-        <v>45612</v>
+        <v>45598</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>100</v>
+      <c r="A57" s="1">
+        <v>10000</v>
       </c>
       <c r="B57" s="2">
-        <v>45612</v>
+        <v>45604</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>99</v>
+        <v>159</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>101</v>
+      <c r="A58" s="1">
+        <v>10000</v>
       </c>
       <c r="B58" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>99</v>
+        <v>159</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B59" s="2">
         <v>45612</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B60" s="2">
-        <v>45618</v>
+        <v>45612</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B61" s="2">
-        <v>45618</v>
+        <v>45612</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B62" s="2">
-        <v>45618</v>
+        <v>45612</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B63" s="2">
         <v>45618</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B65" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="B66" s="2">
-        <v>45626</v>
+        <v>45618</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B67" s="2">
-        <v>45639</v>
+        <v>45626</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B68" s="2">
-        <v>45639</v>
+        <v>45626</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B69" s="2">
-        <v>45639</v>
+        <v>45626</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>114</v>
+      <c r="A70" s="1">
+        <v>10000</v>
       </c>
       <c r="B70" s="2">
-        <v>45931</v>
+        <v>46362</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>37</v>
+        <v>159</v>
+      </c>
+      <c r="E70" s="3">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B71" s="2">
-        <v>45931</v>
+        <v>45639</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>115</v>
+        <v>25</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>45931</v>
+        <v>45639</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B73" s="2">
-        <v>45931</v>
+        <v>45639</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>114</v>
+      <c r="A74" s="1">
+        <v>10000</v>
       </c>
       <c r="B74" s="2">
-        <v>45673</v>
+        <v>45649</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>38</v>
+        <v>159</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B75" s="2">
-        <v>45676</v>
+        <v>45668</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>24</v>
+        <v>95</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B76" s="2">
-        <v>45676</v>
+        <v>45668</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B77" s="2">
-        <v>45676</v>
+        <v>45668</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B78" s="2">
-        <v>45676</v>
+        <v>45668</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="B79" s="2">
-        <v>45872</v>
+        <v>45676</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>12</v>
+        <v>99</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="B80" s="2">
-        <v>45872</v>
+        <v>45676</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="B81" s="2">
-        <v>45872</v>
+        <v>45676</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="B82" s="2">
-        <v>45731</v>
+        <v>45676</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>131</v>
+      <c r="A83" s="1">
+        <v>10000</v>
       </c>
       <c r="B83" s="2">
-        <v>45731</v>
+        <v>45680</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>133</v>
+      <c r="A84" s="1">
+        <v>10000</v>
       </c>
       <c r="B84" s="2">
-        <v>45731</v>
+        <v>46049</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>132</v>
+        <v>159</v>
+      </c>
+      <c r="E84" s="3">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>134</v>
+      <c r="A85" s="1">
+        <v>10000</v>
       </c>
       <c r="B85" s="2">
-        <v>45731</v>
+        <v>46053</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
+      </c>
+      <c r="E85" s="3">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>136</v>
+      <c r="A86" s="1">
+        <v>10000</v>
       </c>
       <c r="B86" s="2">
-        <v>45721</v>
+        <v>46060</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="E86" s="3">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>138</v>
+      <c r="A87" s="1">
+        <v>10000</v>
       </c>
       <c r="B87" s="2">
-        <v>45721</v>
+        <v>46081</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>137</v>
+        <v>159</v>
+      </c>
+      <c r="E87" s="3">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="B88" s="2">
-        <v>45721</v>
+        <v>45724</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="B89" s="2">
-        <v>45875</v>
+        <v>45724</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B90" s="2">
-        <v>45875</v>
+        <v>45724</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="B91" s="2">
-        <v>45875</v>
+        <v>45731</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>57</v>
+        <v>109</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>144</v>
+      <c r="A92" s="1">
+        <v>10000</v>
       </c>
       <c r="B92" s="2">
-        <v>45829</v>
+        <v>45744</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>24</v>
+        <v>159</v>
+      </c>
+      <c r="E92" s="3">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>146</v>
+      <c r="A93" s="1">
+        <v>10000</v>
       </c>
       <c r="B93" s="2">
-        <v>45829</v>
+        <v>45761</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
+      </c>
+      <c r="E93" s="3">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B94" s="2">
-        <v>45829</v>
+        <v>45773</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>148</v>
+        <v>111</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="B95" s="2">
-        <v>45835</v>
+        <v>45773</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="B96" s="2">
-        <v>45835</v>
+        <v>45773</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>150</v>
+      <c r="A97" s="1">
+        <v>10000</v>
       </c>
       <c r="B97" s="2">
-        <v>45835</v>
+        <v>45776</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
+      </c>
+      <c r="E97" s="3">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B98" s="2">
-        <v>45784</v>
+        <v>45780</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>12</v>
+        <v>116</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="B99" s="2">
-        <v>45784</v>
+        <v>45780</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="B100" s="2">
-        <v>45784</v>
+        <v>45780</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
-        <v>94</v>
+      <c r="A101" s="1">
+        <v>10000</v>
       </c>
       <c r="B101" s="2">
-        <v>45907</v>
+        <v>45796</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>38</v>
+        <v>159</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>156</v>
+      <c r="A102" s="1">
+        <v>10000</v>
       </c>
       <c r="B102" s="2">
-        <v>45899</v>
+        <v>45799</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>12</v>
+        <v>134</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>156</v>
+      <c r="A103" s="1">
+        <v>10000</v>
       </c>
       <c r="B103" s="2">
-        <v>45899</v>
+        <v>45801</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
+      </c>
+      <c r="E103" s="3">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="B104" s="2">
-        <v>45899</v>
+        <v>45816</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>82</v>
+        <v>33</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="B105" s="2">
-        <v>45914</v>
+        <v>45816</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="B106" s="2">
-        <v>45914</v>
+        <v>45816</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>159</v>
+        <v>37</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>158</v>
+      <c r="A107" s="1">
+        <v>10000</v>
       </c>
       <c r="B107" s="2">
-        <v>45914</v>
+        <v>45820</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
+      </c>
+      <c r="E107" s="3">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="B108" s="2">
-        <v>45910</v>
+        <v>45829</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>38</v>
+        <v>124</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B109" s="2">
-        <v>46001</v>
+        <v>45829</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="B110" s="2">
-        <v>46001</v>
+        <v>45829</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="B111" s="2">
-        <v>46001</v>
+        <v>45835</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>160</v>
+        <v>128</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B112" s="2">
-        <v>45946</v>
+        <v>45835</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B113" s="2">
-        <v>45949</v>
+        <v>45835</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="B114" s="2">
-        <v>45949</v>
+        <v>45843</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>155</v>
+        <v>131</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="B115" s="2">
-        <v>45949</v>
+        <v>45843</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B116" s="2">
-        <v>45819</v>
+        <v>45843</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="B117" s="2">
-        <v>45972</v>
+        <v>45848</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>24</v>
+        <v>134</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B118" s="2">
-        <v>45972</v>
+        <v>45899</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>168</v>
+        <v>58</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B119" s="2">
-        <v>45972</v>
+        <v>45899</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="B120" s="2">
-        <v>45819</v>
+        <v>45899</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B121" s="2">
-        <v>45819</v>
+        <v>45914</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>38</v>
+        <v>138</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="B122" s="2">
-        <v>45990</v>
+        <v>45914</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="B123" s="2">
-        <v>45990</v>
+        <v>45914</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="B124" s="2">
-        <v>45759</v>
+        <v>46001</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>38</v>
+        <v>138</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="B125" s="2">
-        <v>45973</v>
+        <v>46001</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="B126" s="2">
-        <v>46004</v>
+        <v>46001</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B127" s="2">
-        <v>46004</v>
+        <v>45972</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>48</v>
+        <v>146</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B128" s="2">
-        <v>45759</v>
+        <v>45972</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="B129" s="2">
-        <v>46010</v>
+        <v>45972</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="B130" s="2">
-        <v>46010</v>
+        <v>45990</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>177</v>
+        <v>33</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B131" s="2">
-        <v>46039</v>
+        <v>45990</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="B132" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E133" s="3">
+        <v>3</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46004</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46010</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46010</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46034</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E143" s="3">
+        <v>1</v>
+      </c>
+      <c r="F143" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46038</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E144" s="3">
+        <v>1</v>
+      </c>
+      <c r="F144" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46039</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B146" s="2">
         <v>46047</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E132" s="1">
+      <c r="C146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E146" s="3">
         <v>2</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F146" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" s="1">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46048</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E147" s="3">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46052</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E148" s="3">
+        <v>1</v>
+      </c>
+      <c r="F148" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
         <v>400</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B149" s="2">
         <v>46053</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E133" s="1">
+      <c r="C149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E149" s="3">
         <v>4</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F149" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" s="1">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
         <f>400*0.9</f>
         <v>360</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B150" s="2">
         <v>46053</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>117</v>
+      <c r="C150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E151" s="3">
+        <v>1</v>
+      </c>
+      <c r="F151" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>394</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E152" s="3">
+        <v>1</v>
+      </c>
+      <c r="F152" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A6 A2 C2:I2 A3 C3:I3 A4 C4:I4 A5 C5:I5 A128:I128 A127 C127:I127 A126 C126:I126 A131:I131 A130 C130:I130 A129 C129:I129 A124:I125 A123 C123:I123 A122 C122:I122 A116:I121 A115 C115:I115 A114 C114:I114 A113 C113:I113 A112 C112:I112 A108:I111 A107 C107:I107 A106 C106:I106 A105 C105:I105 A104 C104:I104 A103 C103:I103 A102 C102:I102 A98:I101 A97 C97:I97 A96 C96:I96 A95 C95:I95 A94 C94:I94 A93 C93:I93 A92 C92:I92 A86:I91 A82 C82:I82 A83 C83:I83 A84 C84:I84 A85 C85:I85 A79:I81 A75 C75:I75 A76 C76:I76 A77 C77:I77 A78 C78:I78 A74 C74:I74 A70:I73 A69 C69:I69 A68 C68:I68 A67 C67:I67 A66 C66:I66 A65 C65:I65 A64 C64:I64 A63 C63:I63 A62 C62:I62 A61 C61:I61 A60 C60:I60 A59 C59:I59 A58 C58:I58 A57 C57:I57 A56 C56:I56 A53:I55 A52 C52:I52 A51 C51:I51 A50 C50:I50 A49 C49:I49 A48 C48:I48 A42:I47 A41 C41:I41 A38:I40 A37 C37:I37 A36 C36:I36 A35 C35:I35 A34 C34:I34 A33 C33:I33 A32 C32:I32 A31 C31:I31 A30 C30:I30 A29 C29:I29 A28 C28:I28 A19:I27 A18 C18:I18 A14:I17 A13 C13:I13 A12 C12:I12 A11 C11:I11 A10 C10:I10 A9 C9:I9 A8 C8:I8 A7 C7:I7 C6:I6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A6 A2 C2:F2 A3 C3:F3 A4 C4:F4 A5 C5:F5 A140 A145:F145 A142 C142:F142 A141 C141:F141 A138 A135 A132 C132:F132 A124:F126 A123 C123:F123 A122 C122:F122 A121 C121:F121 A120 C120:F120 A119 C119:F119 A118 C118:F118 A117 A113 C113:F113 A112 C112:F112 A111 C111:F111 A110 C110:F110 A109 C109:F109 A108 C108:F108 A105:A106 A91 C91:F91 A94 C94:F94 A95 C95:F95 A96 C96:F96 A89:A90 A79 C79:F79 A80 C80:F80 A81 C81:F81 A82 C82:F82 A76:A78 A73 C73:F73 A72 C72:F72 A71 C71:F71 A69 C69:F69 A68 C68:F68 A67 C67:F67 A66 C66:F66 A65 C65:F65 A64 C64:F64 A63 C63:F63 A62 C62:F62 A61 C61:F61 A60 C60:F60 A59 C59:F59 A55:A56 A53 C53:F53 A52 C52:F52 A50 C50:F50 A49 C49:F49 A48 C48:F48 A47 A41 C41:F41 A39:A40 A37 C37:F37 A36 C36:F36 A35 C35:F35 A34 C34:F34 A33 C33:F33 A32 C32:F32 A31 C31:F31 A30 C30:F30 A29 C29:F29 A28 C28:F28 A25:A27 A18 C18:F18 A15:A17 A13 C13:F13 A12 C12:F12 A11 C11:F11 A10 C10:F10 A9 C9:F9 A8 C8:F8 A7 C7:F7 C6:F6 A14 C14:F14 C15:F17 A19 C19:F19 A20:A22 C20:F22 A23 C23:F23 A24 C24:F24 C25:F27 A38 C38:F38 C39:F40 A42:A44 C42:F44 A45 C45:F45 A46 C46:F46 C47:F47 A54 C54:F54 C55:F56 A75 C75:F75 C76:F78 A88 E88:F88 E89:F90 C88 C89:C90 A98 C98:F98 A99 C99:F99 A100 C100:F100 A104 C104:F104 C105:F106 A114 C114:F114 A115:A116 C115:F116 C117:F117 A136:A137 A139 C135:F135 C140:F140 C138:F138 C136:F137 C139:E139" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>